--- a/Tach_ChiPhi_PP_BL_KetQua.xlsx
+++ b/Tach_ChiPhi_PP_BL_KetQua.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="164" formatCode="_(* #,##0.0000_);_(* \(#,##0.0000\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <name val="Times New Roman"/>
       <family val="2"/>
@@ -78,6 +78,19 @@
     <font>
       <name val="Times New Roman"/>
       <i val="1"/>
+      <color rgb="001B5E20"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="001B5E20"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <i val="1"/>
       <color rgb="007B3F00"/>
       <sz val="11"/>
     </font>
@@ -89,7 +102,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -100,6 +113,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C8E6C9"/>
       </patternFill>
     </fill>
     <fill>
@@ -258,7 +276,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -393,13 +411,22 @@
     <xf numFmtId="165" fontId="9" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="11" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1206,7 +1233,7 @@
         </is>
       </c>
       <c r="E12" s="38" t="n">
-        <v>919245580</v>
+        <v>948924323</v>
       </c>
       <c r="F12" s="39">
         <f>E12*80.79%</f>
@@ -1248,7 +1275,7 @@
       <c r="A14" s="45" t="n"/>
       <c r="B14" s="45" t="inlineStr">
         <is>
-          <t>Thu hồi VTTB</t>
+          <t>Nhập kho SCL</t>
         </is>
       </c>
       <c r="C14" s="46" t="inlineStr">
@@ -1262,7 +1289,7 @@
         </is>
       </c>
       <c r="E14" s="47" t="n">
-        <v>-29678743</v>
+        <v>29678743</v>
       </c>
       <c r="F14" s="47">
         <f>E14*80.79%</f>
@@ -1519,30 +1546,30 @@
       <c r="H13" s="16" t="n"/>
     </row>
     <row r="14" customFormat="1" s="11">
-      <c r="A14" s="45" t="n"/>
-      <c r="B14" s="45" t="inlineStr">
+      <c r="A14" s="48" t="n"/>
+      <c r="B14" s="48" t="inlineStr">
         <is>
           <t>Thu hồi VTTB</t>
         </is>
       </c>
-      <c r="C14" s="46" t="inlineStr">
+      <c r="C14" s="49" t="inlineStr">
         <is>
           <t>VTAD2606001</t>
         </is>
       </c>
-      <c r="D14" s="46" t="inlineStr">
+      <c r="D14" s="49" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="E14" s="47" t="n">
+      <c r="E14" s="50" t="n">
         <v>-9</v>
       </c>
-      <c r="F14" s="47">
+      <c r="F14" s="50">
         <f>E14*80.79%</f>
         <v/>
       </c>
-      <c r="G14" s="47">
+      <c r="G14" s="50">
         <f>E14-F14</f>
         <v/>
       </c>
@@ -1851,30 +1878,30 @@
       <c r="H15" s="16" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="45" t="n"/>
-      <c r="B16" s="45" t="inlineStr">
+      <c r="A16" s="48" t="n"/>
+      <c r="B16" s="48" t="inlineStr">
         <is>
           <t>Thu hồi VTTB</t>
         </is>
       </c>
-      <c r="C16" s="46" t="inlineStr">
+      <c r="C16" s="49" t="inlineStr">
         <is>
           <t>VTAD2606001</t>
         </is>
       </c>
-      <c r="D16" s="46" t="inlineStr">
+      <c r="D16" s="49" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="E16" s="47" t="n">
+      <c r="E16" s="50" t="n">
         <v>-30</v>
       </c>
-      <c r="F16" s="47">
+      <c r="F16" s="50">
         <f>E16*80.79%</f>
         <v/>
       </c>
-      <c r="G16" s="47">
+      <c r="G16" s="50">
         <f>E16-F16</f>
         <v/>
       </c>
@@ -2245,55 +2272,55 @@
       <c r="H15" s="16" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="45" t="n"/>
-      <c r="B16" s="45" t="inlineStr">
+      <c r="A16" s="48" t="n"/>
+      <c r="B16" s="48" t="inlineStr">
         <is>
           <t>Thu hồi VTTB</t>
         </is>
       </c>
-      <c r="C16" s="46" t="inlineStr">
+      <c r="C16" s="49" t="inlineStr">
         <is>
           <t>VTAD2606001</t>
         </is>
       </c>
-      <c r="D16" s="46" t="inlineStr">
+      <c r="D16" s="49" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="E16" s="47" t="n">
+      <c r="E16" s="50" t="n">
         <v>-8</v>
       </c>
-      <c r="F16" s="47">
+      <c r="F16" s="50">
         <f>E16*80.79%</f>
         <v/>
       </c>
-      <c r="G16" s="47">
+      <c r="G16" s="50">
         <f>E16-F16</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="48" t="n"/>
-      <c r="B17" s="48" t="n"/>
-      <c r="C17" s="49" t="inlineStr">
+      <c r="A17" s="51" t="n"/>
+      <c r="B17" s="51" t="n"/>
+      <c r="C17" s="52" t="inlineStr">
         <is>
           <t>VTAD2606001</t>
         </is>
       </c>
-      <c r="D17" s="49" t="inlineStr">
+      <c r="D17" s="52" t="inlineStr">
         <is>
           <t>Hạ thế</t>
         </is>
       </c>
-      <c r="E17" s="50" t="n">
+      <c r="E17" s="53" t="n">
         <v>-106</v>
       </c>
-      <c r="F17" s="50">
+      <c r="F17" s="53">
         <f>E17*80.79%</f>
         <v/>
       </c>
-      <c r="G17" s="50">
+      <c r="G17" s="53">
         <f>E17-F17</f>
         <v/>
       </c>
@@ -2357,30 +2384,30 @@
       <c r="H19" s="16" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="45" t="n"/>
-      <c r="B20" s="45" t="inlineStr">
+      <c r="A20" s="48" t="n"/>
+      <c r="B20" s="48" t="inlineStr">
         <is>
           <t>Thu hồi VTTB</t>
         </is>
       </c>
-      <c r="C20" s="46" t="inlineStr">
+      <c r="C20" s="49" t="inlineStr">
         <is>
           <t>VTAD2606002</t>
         </is>
       </c>
-      <c r="D20" s="46" t="inlineStr">
+      <c r="D20" s="49" t="inlineStr">
         <is>
           <t>Trung thế</t>
         </is>
       </c>
-      <c r="E20" s="47" t="n">
+      <c r="E20" s="50" t="n">
         <v>-138000</v>
       </c>
-      <c r="F20" s="47">
+      <c r="F20" s="50">
         <f>E20*80.79%</f>
         <v/>
       </c>
-      <c r="G20" s="47">
+      <c r="G20" s="50">
         <f>E20-F20</f>
         <v/>
       </c>
